--- a/data/trans_orig/IP31KM06_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM06_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42125</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31047</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60061</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>48,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28808</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21932</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36635</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45062</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>22946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68651</t>
+          <t>39839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>73023</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60403</t>
+          <t>60138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>91688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80771</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62835</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>91849</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>51,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>74,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>85443</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>77616</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>92319</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>74,79%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91753</t>
+          <t>87699</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68164</t>
+          <t>78759</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105452</t>
+          <t>95652</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>177197</t>
+          <t>168471</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149605</t>
+          <t>149806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>190663</t>
+          <t>181356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>82517</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>70263</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>97857</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>42,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>50421</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>40064</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60954</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>27,09%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85917</t>
+          <t>52241</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72044</t>
+          <t>42106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102185</t>
+          <t>63274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>136338</t>
+          <t>134757</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120011</t>
+          <t>117407</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156069</t>
+          <t>152977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>148724</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>133384</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>160978</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>135693</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>125160</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>146050</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>161603</t>
+          <t>128352</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145335</t>
+          <t>117319</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175476</t>
+          <t>138487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>297296</t>
+          <t>277076</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277565</t>
+          <t>258856</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>313623</t>
+          <t>294426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,49%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70960</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57584</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>84716</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>82520</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60832</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>124533</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>78435</t>
+          <t>56810</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65296</t>
+          <t>46536</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92107</t>
+          <t>66710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>160955</t>
+          <t>127770</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137263</t>
+          <t>112495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216408</t>
+          <t>143614</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>95562</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>81806</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>108938</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,39%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>49,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>65,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>105729</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63716</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>127417</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>56,16%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>104654</t>
+          <t>98228</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90982</t>
+          <t>88328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117793</t>
+          <t>108502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>210384</t>
+          <t>193790</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154931</t>
+          <t>177946</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234076</t>
+          <t>209065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>65,02%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>69581</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>59431</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80622</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>68381</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>58511</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>78519</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>41,56%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>47,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74920</t>
+          <t>71253</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>60723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87727</t>
+          <t>82038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>143302</t>
+          <t>140834</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127780</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160379</t>
+          <t>157215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>96584</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>85543</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>106734</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>96138</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>86000</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>106008</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>58,44%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>52,27%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>102389</t>
+          <t>92726</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89582</t>
+          <t>81941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112911</t>
+          <t>103256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>198526</t>
+          <t>189310</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>181449</t>
+          <t>172929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214048</t>
+          <t>203829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>265182</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>241225</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>291196</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>230130</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>202004</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>287541</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>35,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>284334</t>
+          <t>211202</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254866</t>
+          <t>191598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>315021</t>
+          <t>234513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>514464</t>
+          <t>476384</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>479166</t>
+          <t>444019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>575961</t>
+          <t>512656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>421642</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>395628</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>445599</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>423004</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>365593</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>451130</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>64,77%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>55,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>69,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>460399</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429712</t>
+          <t>383695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489867</t>
+          <t>426610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>883403</t>
+          <t>828647</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>821906</t>
+          <t>792375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>918701</t>
+          <t>861012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
